--- a/activos.xlsx
+++ b/activos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PROYECTOS\SAMA_IA_PROJECT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CAB831F-DD88-4BCA-9E62-10F2D45ADF2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE3C79B8-695E-4474-8333-43B768706FE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
